--- a/resources/ai-for-your-business/files/aifyb-adv-durability-audit.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-adv-durability-audit.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="£#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -616,7 +616,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>working days, no obstruction, no surprise charge</t>
+          <t>business days, no obstruction, no surprise charge</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>IF(COUNTA(B4:B11)&lt;8,"DO NOT PUBLISH - the standard is not fully specified",IF(OR(NOT(ISNUMBER(B6)),NOT(ISNUMBER(B7))),"DO NOT PUBLISH - count the eligible cases and the hits",IF(B6&lt;20,"DO NOT PUBLISH - fewer than 20 eligible cases counted; you cannot know yet",IF(B7&gt;B6,"DO NOT PUBLISH - more hits than cases: check the arithmetic",IF(B7/B6&lt;0.95,"DO NOT PUBLISH - you hit it "&amp;TEXT(B7/B6,"0%")&amp;" of the time. Narrow the scope.",IF(LOWER(TRIM(B8))&lt;&gt;"y","DO NOT PUBLISH - it has not held without you. Narrow the scope.",IF(COUNTA(B9)=0,"DO NOT PUBLISH - name who held it and when",IF(NOT(ISNUMBER(B10)),"DO NOT PUBLISH - record the date you told clients, as a real date","CLEARED to publish")))))))))</f>
+        <f>IF(COUNTA(B4:B11)&lt;8,"DO NOT PUBLISH - the standard is not fully specified",IF(OR(NOT(ISNUMBER(B6)),NOT(ISNUMBER(B7))),"DO NOT PUBLISH - count the eligible cases and the hits",IF(B6&lt;20,"DO NOT PUBLISH - fewer than 20 eligible cases counted; you cannot know yet",IF(B7&gt;B6,"DO NOT PUBLISH - more hits than cases: check the arithmetic",IF(B7/B6&lt;0.95,"DO NOT PUBLISH - you hit it "&amp;TEXT(B7/B6,"0%")&amp;" of the time. Narrow the scope.",IF(LOWER(TRIM(B8))&lt;&gt;"y","DO NOT PUBLISH - it has not held without you. Narrow the scope.",IF(COUNTA(B9)=0,"DO NOT PUBLISH - name who held it and when",IF(NOT(ISNUMBER(B10)),"DO NOT PUBLISH - record the date you told clients, as a real date","CLEARED to publish"))))))))</f>
         <v/>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Your estimated cost of one error (£)</t>
+          <t>Your estimated cost of one error ($)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -910,14 +910,14 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>weekly = 4.3, fortnightly = 2.2, monthly = 1. ⚠️ A CLIENT noticing is not a check.</t>
+          <t>weekly = 4 (the book's example; 4.3 is the exact average), every two weeks = 2, monthly = 1. ⚠️ A CLIENT noticing is not a check.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>What this narrow class earns us per month (£)</t>
+          <t>What this narrow class earns us per month ($)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
@@ -943,7 +943,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>MAXIMUM EXPOSURE per month (£)</t>
+          <t>MAXIMUM EXPOSURE per month ($)</t>
         </is>
       </c>
       <c r="B11" s="8">
@@ -954,7 +954,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>EXPOSURE BUDGET per month (£)</t>
+          <t>EXPOSURE BUDGET per month ($)</t>
         </is>
       </c>
       <c r="B12" s="8">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B36" s="6">
-        <f>IF(OR(NOT(ISNUMBER(B6)),NOT(ISNUMBER(B7)),NOT(ISNUMBER(B8)),B6&lt;=0,B7&lt;=0,B8&lt;=0),"NOT READY - error cost, chances between checks and checks per month must all be above zero. A zero there is a missing answer, not a safe one.",IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(B10)),B9&lt;=0,B10&lt;=0),"NOT READY - what this class earns and the share you can lose must both be above zero, or there is no budget to compare against.",IF(NOT(ISNUMBER(B11)),"NOT READY - exposure not calculated (fill error cost, chances and checks)",IF(NOT(ISNUMBER(B12)),"NOT READY - no exposure budget (fill monthly earnings and the share)",IF(B11&gt;B12,"NOT READY - over the exposure budget: shorten the checking interval",IF(COUNTA(B27:B30)&lt;4,"NOT READY - all four conditions must be written",IF(NOT(ISNUMBER(B31)),"NOT READY - the kill threshold must be a NUMBER, not a phrase",IF(COUNTA(B32)=0,"NOT READY - nobody holds the switch",IF(LOWER(TRIM(B33))&lt;&gt;"y","NOT READY - the holder cannot reach the switch when it matters",IF(NOT(ISNUMBER(B34)),"NOT READY - book the shutdown test as a real DATE","READY - widen this narrow class only"))))))))))</f>
+        <f>IF(OR(NOT(ISNUMBER(B6)),NOT(ISNUMBER(B7)),NOT(ISNUMBER(B8)),B6&lt;=0,B7&lt;=0,B8&lt;=0),"NOT READY - error cost, acts per month and checks per month must all be above zero. A zero there is a missing answer, not a safe one.",IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(B10)),B9&lt;=0,B10&lt;=0),"NOT READY - what this class earns and the share you can lose must both be above zero, or there is no budget to compare against.",IF(NOT(ISNUMBER(B11)),"NOT READY - exposure not calculated (fill error cost, chances and checks)",IF(NOT(ISNUMBER(B12)),"NOT READY - no exposure budget (fill monthly earnings and the share)",IF(B11&gt;B12,"NOT READY - over the exposure budget: shorten the checking interval",IF(COUNTA(B27:B30)&lt;4,"NOT READY - all four conditions must be written",IF(NOT(ISNUMBER(B31)),"NOT READY - the kill threshold must be a NUMBER, not a phrase",IF(COUNTA(B32)=0,"NOT READY - nobody holds the switch",IF(LOWER(TRIM(B33))&lt;&gt;"y","NOT READY - the holder cannot reach the switch when it matters",IF(NOT(ISNUMBER(B34)),"NOT READY - book the shutdown test as a real DATE","READY - widen this narrow class only"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6">
-        <f>IF(OR(COUNTA('1 Thresholds first'!C10)=0,NOT(ISNUMBER('1 Thresholds first'!D10))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B9)=0,COUNT(C9)=0,COUNT(D9)=0),"NOT SCORED - treat as FAIL",IF(OR(B9&lt;&gt;INT(B9),C9&lt;&gt;INT(C9),D9&lt;&gt;INT(D9),B9&lt;0,B9&gt;3,C9&lt;0,C9&gt;3,D9&lt;0,D9&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E9)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G9)=0,COUNTA(H9)=0,NOT(ISNUMBER(I9))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G9))=LOWER(TRIM(H9)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I9&lt;='1 Thresholds first'!D10,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B9,C9)&lt;D9,"FLAGGED - go to chapter 9","clear"))))))))))</f>
+        <f>IF(OR(COUNTA('1 Thresholds first'!C10)=0,NOT(ISNUMBER('1 Thresholds first'!D10))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B9)=0,COUNT(C9)=0,COUNT(D9)=0),"NOT SCORED - treat as FAIL",IF(OR(B9&lt;&gt;INT(B9),C9&lt;&gt;INT(C9),D9&lt;&gt;INT(D9),B9&lt;0,B9&gt;3,C9&lt;0,C9&gt;3,D9&lt;0,D9&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E9)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G9)=0,COUNTA(H9)=0,NOT(ISNUMBER(I9))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G9))=LOWER(TRIM(H9)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I9&lt;='1 Thresholds first'!D10,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B9,C9)&lt;D9,"FLAGGED - go to chapter 9","clear"))))))))</f>
         <v/>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="6">
-        <f>IF(OR(COUNTA('1 Thresholds first'!C11)=0,NOT(ISNUMBER('1 Thresholds first'!D11))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B10)=0,COUNT(C10)=0,COUNT(D10)=0),"NOT SCORED - treat as FAIL",IF(OR(B10&lt;&gt;INT(B10),C10&lt;&gt;INT(C10),D10&lt;&gt;INT(D10),B10&lt;0,B10&gt;3,C10&lt;0,C10&gt;3,D10&lt;0,D10&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E10)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G10)=0,COUNTA(H10)=0,NOT(ISNUMBER(I10))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G10))=LOWER(TRIM(H10)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I10&lt;='1 Thresholds first'!D11,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B10,C10)&lt;D10,"FLAGGED - go to chapter 9","clear"))))))))))</f>
+        <f>IF(OR(COUNTA('1 Thresholds first'!C11)=0,NOT(ISNUMBER('1 Thresholds first'!D11))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B10)=0,COUNT(C10)=0,COUNT(D10)=0),"NOT SCORED - treat as FAIL",IF(OR(B10&lt;&gt;INT(B10),C10&lt;&gt;INT(C10),D10&lt;&gt;INT(D10),B10&lt;0,B10&gt;3,C10&lt;0,C10&gt;3,D10&lt;0,D10&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E10)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G10)=0,COUNTA(H10)=0,NOT(ISNUMBER(I10))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G10))=LOWER(TRIM(H10)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I10&lt;='1 Thresholds first'!D11,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B10,C10)&lt;D10,"FLAGGED - go to chapter 9","clear"))))))))</f>
         <v/>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="6">
-        <f>IF(OR(COUNTA('1 Thresholds first'!C12)=0,NOT(ISNUMBER('1 Thresholds first'!D12))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B11)=0,COUNT(C11)=0,COUNT(D11)=0),"NOT SCORED - treat as FAIL",IF(OR(B11&lt;&gt;INT(B11),C11&lt;&gt;INT(C11),D11&lt;&gt;INT(D11),B11&lt;0,B11&gt;3,C11&lt;0,C11&gt;3,D11&lt;0,D11&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E11)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G11)=0,COUNTA(H11)=0,NOT(ISNUMBER(I11))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G11))=LOWER(TRIM(H11)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I11&lt;='1 Thresholds first'!D12,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B11,C11)&lt;D11,"FLAGGED - go to chapter 9","clear"))))))))))</f>
+        <f>IF(OR(COUNTA('1 Thresholds first'!C12)=0,NOT(ISNUMBER('1 Thresholds first'!D12))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B11)=0,COUNT(C11)=0,COUNT(D11)=0),"NOT SCORED - treat as FAIL",IF(OR(B11&lt;&gt;INT(B11),C11&lt;&gt;INT(C11),D11&lt;&gt;INT(D11),B11&lt;0,B11&gt;3,C11&lt;0,C11&gt;3,D11&lt;0,D11&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E11)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G11)=0,COUNTA(H11)=0,NOT(ISNUMBER(I11))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G11))=LOWER(TRIM(H11)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I11&lt;='1 Thresholds first'!D12,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B11,C11)&lt;D11,"FLAGGED - go to chapter 9","clear"))))))))</f>
         <v/>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="6">
-        <f>IF(OR(COUNTA('1 Thresholds first'!C13)=0,NOT(ISNUMBER('1 Thresholds first'!D13))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B12)=0,COUNT(C12)=0,COUNT(D12)=0),"NOT SCORED - treat as FAIL",IF(OR(B12&lt;&gt;INT(B12),C12&lt;&gt;INT(C12),D12&lt;&gt;INT(D12),B12&lt;0,B12&gt;3,C12&lt;0,C12&gt;3,D12&lt;0,D12&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E12)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G12)=0,COUNTA(H12)=0,NOT(ISNUMBER(I12))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G12))=LOWER(TRIM(H12)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I12&lt;='1 Thresholds first'!D13,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B12,C12)&lt;D12,"FLAGGED - go to chapter 9","clear"))))))))))</f>
+        <f>IF(OR(COUNTA('1 Thresholds first'!C13)=0,NOT(ISNUMBER('1 Thresholds first'!D13))),"NOT PRE-REGISTERED - treat as FAIL. Write what evidence you will accept, and date it, BEFORE scoring.",IF(OR(COUNT(B12)=0,COUNT(C12)=0,COUNT(D12)=0),"NOT SCORED - treat as FAIL",IF(OR(B12&lt;&gt;INT(B12),C12&lt;&gt;INT(C12),D12&lt;&gt;INT(D12),B12&lt;0,B12&gt;3,C12&lt;0,C12&gt;3,D12&lt;0,D12&gt;3),"NOT SCORED - scores and thresholds must be whole numbers from 0 to 3",IF(COUNTA(E12)=0,"NOT EVIDENCED - treat as FAIL. What did you look at?",IF(OR(COUNTA(G12)=0,COUNTA(H12)=0,NOT(ISNUMBER(I12))),"NOT SIGNED - treat as FAIL. Both scorers must be named, with a date.",IF(LOWER(TRIM(G12))=LOWER(TRIM(H12)),"NOT INDEPENDENT - treat as FAIL. One person cannot be both scorers.",IF(I12&lt;='1 Thresholds first'!D13,"OUT OF ORDER - treat as FAIL. The threshold is dated on or after the scoring, so it was not pre-registered.",IF(MIN(B12,C12)&lt;D12,"FLAGGED - go to chapter 9","clear"))))))))</f>
         <v/>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -1991,49 +1991,49 @@
     </row>
     <row r="21">
       <c r="A21" s="6">
-        <f>IF(COUNTA(A9)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A9)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B9)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B9))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B9))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B9))="de-risk",IF(OR(COUNTA(C9)=0,COUNTA(D9)=0,NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D9)=0,NOT(ISNUMBER(E9))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B9))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A9)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A9)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B9)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B9))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A9,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C9)=0,COUNTA(D9)=0,NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B9))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B9))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A9,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B9))="de-risk",IF(OR(COUNTA(C9)=0,COUNTA(D9)=0,NOT(ISNUMBER(E9)),NOT(ISNUMBER(F9))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D9)=0,NOT(ISNUMBER(E9))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B9))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6">
-        <f>IF(COUNTA(A10)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A10)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B10)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B10))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B10))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B10))="de-risk",IF(OR(COUNTA(C10)=0,COUNTA(D10)=0,NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D10)=0,NOT(ISNUMBER(E10))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B10))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A10)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A10)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B10)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B10))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A10,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C10)=0,COUNTA(D10)=0,NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B10))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B10))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A10,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B10))="de-risk",IF(OR(COUNTA(C10)=0,COUNTA(D10)=0,NOT(ISNUMBER(E10)),NOT(ISNUMBER(F10))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D10)=0,NOT(ISNUMBER(E10))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B10))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6">
-        <f>IF(COUNTA(A11)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A11)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B11)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B11))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B11))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B11))="de-risk",IF(OR(COUNTA(C11)=0,COUNTA(D11)=0,NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D11)=0,NOT(ISNUMBER(E11))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B11))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A11)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A11)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B11)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B11))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A11,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C11)=0,COUNTA(D11)=0,NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B11))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B11))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A11,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B11))="de-risk",IF(OR(COUNTA(C11)=0,COUNTA(D11)=0,NOT(ISNUMBER(E11)),NOT(ISNUMBER(F11))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D11)=0,NOT(ISNUMBER(E11))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B11))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6">
-        <f>IF(COUNTA(A12)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A12)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B12)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B12))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B12))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B12))="de-risk",IF(OR(COUNTA(C12)=0,COUNTA(D12)=0,NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D12)=0,NOT(ISNUMBER(E12))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B12))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A12)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A12)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B12)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B12))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A12,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C12)=0,COUNTA(D12)=0,NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B12))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B12))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A12,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B12))="de-risk",IF(OR(COUNTA(C12)=0,COUNTA(D12)=0,NOT(ISNUMBER(E12)),NOT(ISNUMBER(F12))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D12)=0,NOT(ISNUMBER(E12))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B12))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6">
-        <f>IF(COUNTA(A13)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A13)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B13)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B13))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B13))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B13))="de-risk",IF(OR(COUNTA(C13)=0,COUNTA(D13)=0,NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D13)=0,NOT(ISNUMBER(E13))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B13))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A13)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A13)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B13)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B13))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A13,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C13)=0,COUNTA(D13)=0,NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B13))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B13))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A13,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B13))="de-risk",IF(OR(COUNTA(C13)=0,COUNTA(D13)=0,NOT(ISNUMBER(E13)),NOT(ISNUMBER(F13))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D13)=0,NOT(ISNUMBER(E13))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B13))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6">
-        <f>IF(COUNTA(A14)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A14)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B14)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B14))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B14))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B14))="de-risk",IF(OR(COUNTA(C14)=0,COUNTA(D14)=0,NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D14)=0,NOT(ISNUMBER(E14))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B14))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A14)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A14)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B14)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B14))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A14,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C14)=0,COUNTA(D14)=0,NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B14))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B14))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A14,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B14))="de-risk",IF(OR(COUNTA(C14)=0,COUNTA(D14)=0,NOT(ISNUMBER(E14)),NOT(ISNUMBER(F14))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D14)=0,NOT(ISNUMBER(E14))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B14))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <f>IF(COUNTA(A15)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A15)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B15)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B15))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B15))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B15))="de-risk",IF(OR(COUNTA(C15)=0,COUNTA(D15)=0,NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D15)=0,NOT(ISNUMBER(E15))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B15))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A15)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A15)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B15)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B15))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A15,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C15)=0,COUNTA(D15)=0,NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B15))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B15))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A15,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B15))="de-risk",IF(OR(COUNTA(C15)=0,COUNTA(D15)=0,NOT(ISNUMBER(E15)),NOT(ISNUMBER(F15))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D15)=0,NOT(ISNUMBER(E15))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B15))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6">
-        <f>IF(COUNTA(A16)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A16)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B16)=0,"FAIL - no verb chosen",IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B16))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B16))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B16))="de-risk",IF(OR(COUNTA(C16)=0,COUNTA(D16)=0,NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D16)=0,NOT(ISNUMBER(E16))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B16))&amp;", owned and dated"))))))))</f>
+        <f>IF(COUNTA(A16)=0,"",IF(COUNTIF('2 Score it'!$A$9:$A$12,A16)=0,"FAIL - that is not one of the four gates",IF(COUNTA(B16)=0,"FAIL - no verb chosen",IF(AND(LOWER(TRIM(B16))="de-risk",INDEX('2 Score it'!$F$9:$F$12,MATCH(A16,'2 Score it'!$A$9:$A$12,0))="clear"),IF(OR(COUNTA(C16)=0,COUNTA(D16)=0,NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(COUNTA(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0)))=0,"FAIL - no verb was pre-registered for this gate. Go back to sheet 1.",IF(AND(LOWER(TRIM(B16))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0)))),LOWER(TRIM(B16))&lt;&gt;LOWER(TRIM(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A16,'1 Thresholds first'!$A$17:$A$20,0))))),"FAIL - that is not a verb you pre-registered for this gate",IF(LOWER(TRIM(B16))="de-risk",IF(OR(COUNTA(C16)=0,COUNTA(D16)=0,NOT(ISNUMBER(E16)),NOT(ISNUMBER(F16))),"DEFERRAL, not a de-risk - it needs a control, an owner, a live DATE and a re-score DATE","valid de-risk"),IF(OR(COUNTA(D16)=0,NOT(ISNUMBER(E16))),"FAIL - every decision needs an owner and a real date","ok - "&amp;LOWER(TRIM(B16))&amp;", owned and dated"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(COUNTA(B33)=0,"NOT SCORED - treat as FAIL",IF(B33="clear","not flagged - nothing owed",IF(C33=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
+        <f>IF(COUNTA(B33)=0,"NOT SCORED - treat as FAIL",IF(B33="clear","clear - nothing owed",IF(C33=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A33,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A33,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
         <v/>
       </c>
       <c r="E33" s="6">
@@ -2108,7 +2108,7 @@
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(COUNTA(B34)=0,"NOT SCORED - treat as FAIL",IF(B34="clear","not flagged - nothing owed",IF(C34=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
+        <f>IF(COUNTA(B34)=0,"NOT SCORED - treat as FAIL",IF(B34="clear","clear - nothing owed",IF(C34=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A34,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A34,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
         <v/>
       </c>
       <c r="E34" s="6">
@@ -2130,7 +2130,7 @@
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(COUNTA(B35)=0,"NOT SCORED - treat as FAIL",IF(B35="clear","not flagged - nothing owed",IF(C35=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
+        <f>IF(COUNTA(B35)=0,"NOT SCORED - treat as FAIL",IF(B35="clear","clear - nothing owed",IF(C35=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A35,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A35,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
         <v/>
       </c>
       <c r="E35" s="6">
@@ -2152,7 +2152,7 @@
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(COUNTA(B36)=0,"NOT SCORED - treat as FAIL",IF(B36="clear","not flagged - nothing owed",IF(C36=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
+        <f>IF(COUNTA(B36)=0,"NOT SCORED - treat as FAIL",IF(B36="clear","clear - nothing owed",IF(C36=0,"NOT COVERED - no verb was pre-registered for this gate",IF(LEFT(INDEX('1 Thresholds first'!$E$17:$E$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),15)="NOT TWO ACTIONS","NOT COVERED - the pre-registration for this gate is invalid: its second verb repeats the first. Fix sheet 1.",IF(COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0,"NOT COVERED - the pre-registered verb "&amp;INDEX('1 Thresholds first'!$B$17:$B$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0))&amp;" has no complete decision",IF(AND(COUNTA(INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)))&gt;0,COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"ok*")+COUNTIFS($A$9:$A$16,A36,$B$9:$B$16,INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0)),$A$21:$A$28,"valid*")=0),"NOT COVERED - you also obliged "&amp;INDEX('1 Thresholds first'!$C$17:$C$20,MATCH(A36,'1 Thresholds first'!$A$17:$A$20,0))&amp;" here, and it has no complete decision","covered"))))))</f>
         <v/>
       </c>
       <c r="E36" s="6">
@@ -2174,7 +2174,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>If a client reorganised around what you are changing: tell them yourself and early,</t>
+          <t>If a client reorganized around what you are changing: tell them yourself and early,</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>90 minutes. Three people, one of whom is not you: the candidate owner, the checker,</t>
+          <t>90 minutes. Four roles across at least three people, one of whom is not you: the candidate owner, the checker,</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>⚠️ It may NOT conclude 'all fine, see you in three months'.</t>
+          <t>⚠️ 'Continue unchanged' is a valid result ONLY when every gate scores 3 -- record it as a decision, with the evidence.</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Decision (revise / threshold / narrow / cap / retire / promote / investigate / continue unchanged)</t>
+          <t>Decision (pick from the list: revise the rule / move a threshold / narrow / cap / retire / promote a deferred candidate / commission an investigation / continue unchanged / unresolved - reconvene / provisional - role missing)</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2462,7 +2462,7 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="6">
-        <f>IF(COUNTA(A28)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A28)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA(B28)*COUNTA(C28)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(E28))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E28&lt;=D28,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A28))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))</f>
+        <f>IF(COUNTA(A28)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A28)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged","unresolved - reconvene","provisional - role missing"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA($B$31)=0,"INCOMPLETE - say whether all four roles were in the room (y/n)",IF(AND(LOWER(TRIM($B$31))&lt;&gt;"y",LOWER(TRIM(A28))&lt;&gt;"provisional - role missing"),"NOT ALLOWED - a role was missing, so only a provisional record: what you could not decide, and when you will",IF(AND(LOWER(TRIM($B$31))="y",LOWER(TRIM(A28))="provisional - role missing"),"NOT ALLOWED - all four roles were present, so decide",IF(COUNTA(B28)*COUNTA(C28)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(E28))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E28&lt;=D28,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A28))="unresolved - reconvene",E28-D28&gt;31),"INCOMPLETE - an unresolved deadlock reconvenes inside a month",IF(AND(LOWER(TRIM(A28))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="6">
-        <f>IF(COUNTA(A29)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A29)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA(B29)*COUNTA(C29)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(E29))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E29&lt;=D29,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A29))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))</f>
+        <f>IF(COUNTA(A29)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A29)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged","unresolved - reconvene","provisional - role missing"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA($B$31)=0,"INCOMPLETE - say whether all four roles were in the room (y/n)",IF(AND(LOWER(TRIM($B$31))&lt;&gt;"y",LOWER(TRIM(A29))&lt;&gt;"provisional - role missing"),"NOT ALLOWED - a role was missing, so only a provisional record: what you could not decide, and when you will",IF(AND(LOWER(TRIM($B$31))="y",LOWER(TRIM(A29))="provisional - role missing"),"NOT ALLOWED - all four roles were present, so decide",IF(COUNTA(B29)*COUNTA(C29)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(E29))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E29&lt;=D29,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A29))="unresolved - reconvene",E29-D29&gt;31),"INCOMPLETE - an unresolved deadlock reconvenes inside a month",IF(AND(LOWER(TRIM(A29))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -2484,9 +2484,17 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="6">
-        <f>IF(COUNTA(A30)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A30)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA(B30)*COUNTA(C30)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(E30))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E30&lt;=D30,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A30))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))</f>
-        <v/>
-      </c>
+        <f>IF(COUNTA(A30)=0,"",IF(ISNA(MATCH(LOWER(TRIM(A30)),{"revise the rule","move a threshold","narrow","cap","retire","promote a deferred candidate","commission an investigation","continue unchanged","unresolved - reconvene","provisional - role missing"},0)),"NOT ALLOWED - that is not one of the permitted decisions",IF(COUNTA($B$31)=0,"INCOMPLETE - say whether all four roles were in the room (y/n)",IF(AND(LOWER(TRIM($B$31))&lt;&gt;"y",LOWER(TRIM(A30))&lt;&gt;"provisional - role missing"),"NOT ALLOWED - a role was missing, so only a provisional record: what you could not decide, and when you will",IF(AND(LOWER(TRIM($B$31))="y",LOWER(TRIM(A30))="provisional - role missing"),"NOT ALLOWED - all four roles were present, so decide",IF(COUNTA(B30)*COUNTA(C30)=0,"INCOMPLETE - needs evidence and an owner",IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(E30))),"INCOMPLETE - the decision date and the next review must both be real dates",IF(E30&lt;=D30,"INCOMPLETE - the next review must come after the decision",IF(AND(LOWER(TRIM(A30))="unresolved - reconvene",E30-D30&gt;31),"INCOMPLETE - an unresolved deadlock reconvenes inside a month",IF(AND(LOWER(TRIM(A30))="continue unchanged",OR(COUNTIF('2 Score it'!$F$9:$F$12,"clear")&lt;4,MIN('2 Score it'!$B$9:$C$12)&lt;3)),"NOT ALLOWED - continue unchanged needs all four gates clear AND every score at 3. A low threshold does not make a low score acceptable.","recorded"))))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>All four roles in the room? (y/n)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2516,7 +2524,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>other. What is banned is adjourning without recording anything.</t>
+          <t>other. A deadlock nothing governs is 'unresolved - reconvene' (change nothing, back within a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>month); a missing role is 'provisional - role missing'. Neither is 'continue unchanged'.</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2585,15 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D28:E30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Enter a real date" error="Type a date. 'Soon' and 'later' are not dates, and the gate checks for a real one." type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="A28:A30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of: revise the rule,move a threshold,narrow,cap,retire,promote a deferred candidate,commission an investigation,continue unchanged" type="list">
-      <formula1>"revise the rule,move a threshold,narrow,cap,retire,promote a deferred candidate,commission an investigation,continue unchanged"</formula1>
+    <dataValidation sqref="A28:A30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of: revise the rule,move a threshold,narrow,cap,retire,promote a deferred candidate,commission an investigation,continue unchanged,unresolved - reconvene,provisional - role missing" type="list">
+      <formula1>"revise the rule,move a threshold,narrow,cap,retire,promote a deferred candidate,commission an investigation,continue unchanged,unresolved - reconvene,provisional - role missing"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of: y,n" type="list">
+      <formula1>"y,n"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/ai-for-your-business/files/aifyb-adv-durability-audit.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-adv-durability-audit.xlsx
@@ -804,7 +804,7 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
